--- a/branches/fix/termserv-secret-names/ValueSet-von-seltene-betroffen-vs.xlsx
+++ b/branches/fix/termserv-secret-names/ValueSet-von-seltene-betroffen-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:45:00+00:00</t>
+    <t>2026-09-01T21:00:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
